--- a/slide_classification/TCGA_Results/Caption_based_aggregation_15_classes/H-Optimus-1/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
+++ b/slide_classification/TCGA_Results/Caption_based_aggregation_15_classes/H-Optimus-1/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
@@ -609,7 +609,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -695,7 +695,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -738,7 +738,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
@@ -953,7 +953,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -3014,10 +3014,10 @@
         <v>0.552554</v>
       </c>
       <c r="H60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>0.666667</v>
+        <v>0.333333</v>
       </c>
       <c r="J60" t="n">
         <v>1</v>
@@ -3146,7 +3146,7 @@
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J63" t="n">
         <v>1</v>
@@ -3189,7 +3189,7 @@
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -3745,10 +3745,10 @@
         <v>0.9101359999999999</v>
       </c>
       <c r="H77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>0.666667</v>
+        <v>0.333333</v>
       </c>
       <c r="J77" t="n">
         <v>1</v>
@@ -3788,10 +3788,10 @@
         <v>0.652715</v>
       </c>
       <c r="H78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>0.666667</v>
+        <v>0.333333</v>
       </c>
       <c r="J78" t="n">
         <v>1</v>
@@ -4694,7 +4694,7 @@
         <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J99" t="n">
         <v>1</v>
@@ -4737,7 +4737,7 @@
         <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -5078,10 +5078,10 @@
         <v>0.998312</v>
       </c>
       <c r="H108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I108" t="n">
-        <v>0.333333</v>
+        <v>0.666667</v>
       </c>
       <c r="J108" t="n">
         <v>1</v>
@@ -6113,7 +6113,7 @@
         <v>0</v>
       </c>
       <c r="I132" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -6672,7 +6672,7 @@
         <v>0</v>
       </c>
       <c r="I145" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -8564,7 +8564,7 @@
         <v>0</v>
       </c>
       <c r="I189" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -8736,7 +8736,7 @@
         <v>0</v>
       </c>
       <c r="I193" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J193" t="n">
         <v>1</v>
@@ -9292,10 +9292,10 @@
         <v>0.706356</v>
       </c>
       <c r="H206" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I206" t="n">
-        <v>0.666667</v>
+        <v>0.333333</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -9338,7 +9338,7 @@
         <v>0</v>
       </c>
       <c r="I207" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -9381,7 +9381,7 @@
         <v>0</v>
       </c>
       <c r="I208" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -10241,7 +10241,7 @@
         <v>0</v>
       </c>
       <c r="I228" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -11144,7 +11144,7 @@
         <v>0</v>
       </c>
       <c r="I249" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J249" t="n">
         <v>1</v>
@@ -11187,7 +11187,7 @@
         <v>0</v>
       </c>
       <c r="I250" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -11660,7 +11660,7 @@
         <v>0</v>
       </c>
       <c r="I261" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -11786,10 +11786,10 @@
         <v>0.986905</v>
       </c>
       <c r="H264" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I264" t="n">
-        <v>0.666667</v>
+        <v>0.333333</v>
       </c>
       <c r="J264" t="n">
         <v>1</v>
@@ -12133,7 +12133,7 @@
         <v>0</v>
       </c>
       <c r="I272" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J272" t="n">
         <v>0</v>
@@ -13592,10 +13592,10 @@
         <v>0.265261</v>
       </c>
       <c r="H306" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I306" t="n">
-        <v>0.333333</v>
+        <v>0.666667</v>
       </c>
       <c r="J306" t="n">
         <v>0</v>

--- a/slide_classification/TCGA_Results/Caption_based_aggregation_15_classes/H-Optimus-1/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
+++ b/slide_classification/TCGA_Results/Caption_based_aggregation_15_classes/H-Optimus-1/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
@@ -517,7 +517,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.184401</v>
+        <v>0.12871</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -560,7 +560,7 @@
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.980494</v>
+        <v>0.994702</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -603,7 +603,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.411975</v>
+        <v>0.14231</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -643,10 +643,10 @@
         <v>4.2e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.517397</v>
+        <v>0.34363</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -689,7 +689,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.277299</v>
+        <v>0.175029</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -729,10 +729,10 @@
         <v>0.048111</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.756258</v>
+        <v>0.399662</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -775,7 +775,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.280983</v>
+        <v>0.146662</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -818,7 +818,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.149682</v>
+        <v>0.09955</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.327341</v>
+        <v>0.179668</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -904,7 +904,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.178469</v>
+        <v>0.099811</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -944,10 +944,10 @@
         <v>1e-06</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.783624</v>
+        <v>0.495952</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -990,7 +990,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.173114</v>
+        <v>0.097218</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1033,7 +1033,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.47633</v>
+        <v>0.260936</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1076,7 +1076,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.308061</v>
+        <v>0.179836</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1116,10 +1116,10 @@
         <v>0.995129</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.606063</v>
+        <v>0.484633</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1162,7 +1162,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.291108</v>
+        <v>0.116226</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1205,7 +1205,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.180732</v>
+        <v>0.109126</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1248,7 +1248,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.197721</v>
+        <v>0.107646</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1291,7 +1291,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.172828</v>
+        <v>0.109692</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.202532</v>
+        <v>0.121185</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1377,7 +1377,7 @@
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>0.899717</v>
+        <v>0.925967</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1420,7 +1420,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.29454</v>
+        <v>0.106542</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1463,7 +1463,7 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.305038</v>
+        <v>0.132002</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1506,7 +1506,7 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.440075</v>
+        <v>0.213949</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1549,7 +1549,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0.374472</v>
+        <v>0.183393</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.440832</v>
+        <v>0.229838</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1632,10 +1632,10 @@
         <v>7.2e-05</v>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.574532</v>
+        <v>0.454937</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1678,7 +1678,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.413307</v>
+        <v>0.293803</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1721,7 +1721,7 @@
         <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>0.945735</v>
+        <v>0.967261</v>
       </c>
       <c r="H30" t="n">
         <v>1</v>
@@ -1764,7 +1764,7 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.246848</v>
+        <v>0.105192</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1807,7 +1807,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.41113</v>
+        <v>0.176861</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1847,10 +1847,10 @@
         <v>0.202124</v>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.507122</v>
+        <v>0.20507</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1890,10 +1890,10 @@
         <v>0.000158</v>
       </c>
       <c r="F34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.654199</v>
+        <v>0.465303</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1936,7 +1936,7 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0.321942</v>
+        <v>0.190537</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1979,7 +1979,7 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0.324219</v>
+        <v>0.145337</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -2022,7 +2022,7 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0.325044</v>
+        <v>0.17724</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -2065,7 +2065,7 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0.300333</v>
+        <v>0.17577</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2108,7 +2108,7 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0.212602</v>
+        <v>0.118025</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -2151,7 +2151,7 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.196931</v>
+        <v>0.092988</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0.28037</v>
+        <v>0.176226</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0.227835</v>
+        <v>0.111961</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -2280,7 +2280,7 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0.289904</v>
+        <v>0.153042</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0.376359</v>
+        <v>0.154403</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -2363,10 +2363,10 @@
         <v>0.85321</v>
       </c>
       <c r="F45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0.615615</v>
+        <v>0.437891</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -2409,7 +2409,7 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0.397116</v>
+        <v>0.371268</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -2452,7 +2452,7 @@
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>0.345433</v>
+        <v>0.152468</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -2492,10 +2492,10 @@
         <v>0.033914</v>
       </c>
       <c r="F48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>0.504481</v>
+        <v>0.23042</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -2535,10 +2535,10 @@
         <v>2e-05</v>
       </c>
       <c r="F49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>0.50057</v>
+        <v>0.287737</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -2581,7 +2581,7 @@
         <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>0.615382</v>
+        <v>0.525775</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -2621,10 +2621,10 @@
         <v>0.032327</v>
       </c>
       <c r="F51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>0.717597</v>
+        <v>0.461383</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -2667,7 +2667,7 @@
         <v>1</v>
       </c>
       <c r="G52" t="n">
-        <v>0.927941</v>
+        <v>0.919041</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -2710,7 +2710,7 @@
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>0.370323</v>
+        <v>0.166425</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -2750,10 +2750,10 @@
         <v>5e-06</v>
       </c>
       <c r="F54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>0.544647</v>
+        <v>0.19216</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -2793,10 +2793,10 @@
         <v>0.213161</v>
       </c>
       <c r="F55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>0.753076</v>
+        <v>0.485916</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -2839,7 +2839,7 @@
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>0.128443</v>
+        <v>0.067037</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -2879,10 +2879,10 @@
         <v>5e-06</v>
       </c>
       <c r="F57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>0.529127</v>
+        <v>0.23171</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -2925,7 +2925,7 @@
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>0.235469</v>
+        <v>0.157102</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -2968,7 +2968,7 @@
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>0.438491</v>
+        <v>0.359525</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -3008,10 +3008,10 @@
         <v>4e-06</v>
       </c>
       <c r="F60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>0.552554</v>
+        <v>0.322935</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
         <v>1</v>
       </c>
       <c r="G61" t="n">
-        <v>0.990027</v>
+        <v>0.997217</v>
       </c>
       <c r="H61" t="n">
         <v>1</v>
@@ -3094,10 +3094,10 @@
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>0.552242</v>
+        <v>0.312584</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
@@ -3140,7 +3140,7 @@
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>0.977504</v>
+        <v>0.988192</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -3183,7 +3183,7 @@
         <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>0.4299</v>
+        <v>0.242567</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -3223,10 +3223,10 @@
         <v>4e-06</v>
       </c>
       <c r="F65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>0.513026</v>
+        <v>0.334688</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -3269,7 +3269,7 @@
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>0.222517</v>
+        <v>0.104968</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -3312,7 +3312,7 @@
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>0.335942</v>
+        <v>0.204627</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -3355,7 +3355,7 @@
         <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>0.458403</v>
+        <v>0.232325</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -3398,7 +3398,7 @@
         <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>0.282359</v>
+        <v>0.10631</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -3441,7 +3441,7 @@
         <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>0.151236</v>
+        <v>0.070159</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>0.488725</v>
+        <v>0.310365</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>0.283826</v>
+        <v>0.09049699999999999</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -3570,7 +3570,7 @@
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>0.363383</v>
+        <v>0.161663</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -3613,7 +3613,7 @@
         <v>1</v>
       </c>
       <c r="G74" t="n">
-        <v>0.830267</v>
+        <v>0.830719</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -3656,7 +3656,7 @@
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>0.438401</v>
+        <v>0.327721</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -3699,7 +3699,7 @@
         <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>0.413267</v>
+        <v>0.212401</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -3742,7 +3742,7 @@
         <v>1</v>
       </c>
       <c r="G77" t="n">
-        <v>0.9101359999999999</v>
+        <v>0.98837</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -3785,7 +3785,7 @@
         <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>0.652715</v>
+        <v>0.648654</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -3828,7 +3828,7 @@
         <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>0.444793</v>
+        <v>0.250948</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
@@ -3871,7 +3871,7 @@
         <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>0.428672</v>
+        <v>0.334615</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -3914,7 +3914,7 @@
         <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>0.23162</v>
+        <v>0.150382</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -3957,7 +3957,7 @@
         <v>1</v>
       </c>
       <c r="G82" t="n">
-        <v>0.809122</v>
+        <v>0.8913</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
@@ -4000,7 +4000,7 @@
         <v>1</v>
       </c>
       <c r="G83" t="n">
-        <v>0.598682</v>
+        <v>0.6803940000000001</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -4043,7 +4043,7 @@
         <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>0.247997</v>
+        <v>0.106581</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -4086,7 +4086,7 @@
         <v>0</v>
       </c>
       <c r="G85" t="n">
-        <v>0.179792</v>
+        <v>0.102255</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -4126,10 +4126,10 @@
         <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>0.661178</v>
+        <v>0.33917</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -4172,7 +4172,7 @@
         <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>0.195906</v>
+        <v>0.084732</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -4215,7 +4215,7 @@
         <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>0.292049</v>
+        <v>0.114697</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -4258,7 +4258,7 @@
         <v>1</v>
       </c>
       <c r="G89" t="n">
-        <v>0.97234</v>
+        <v>0.996076</v>
       </c>
       <c r="H89" t="n">
         <v>1</v>
@@ -4301,7 +4301,7 @@
         <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>0.067943</v>
+        <v>0.036785</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>0.258343</v>
+        <v>0.093726</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -4387,7 +4387,7 @@
         <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>0.266652</v>
+        <v>0.127831</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
@@ -4430,7 +4430,7 @@
         <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>0.306259</v>
+        <v>0.12981</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -4473,7 +4473,7 @@
         <v>0</v>
       </c>
       <c r="G94" t="n">
-        <v>0.373713</v>
+        <v>0.186616</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>0.418612</v>
+        <v>0.206864</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -4556,10 +4556,10 @@
         <v>8.1e-05</v>
       </c>
       <c r="F96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>0.5344100000000001</v>
+        <v>0.2331</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -4602,7 +4602,7 @@
         <v>0</v>
       </c>
       <c r="G97" t="n">
-        <v>0.36918</v>
+        <v>0.187686</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
@@ -4645,7 +4645,7 @@
         <v>1</v>
       </c>
       <c r="G98" t="n">
-        <v>0.645629</v>
+        <v>0.613787</v>
       </c>
       <c r="H98" t="n">
         <v>1</v>
@@ -4688,7 +4688,7 @@
         <v>1</v>
       </c>
       <c r="G99" t="n">
-        <v>0.9791879999999999</v>
+        <v>0.992469</v>
       </c>
       <c r="H99" t="n">
         <v>0</v>
@@ -4728,10 +4728,10 @@
         <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G100" t="n">
-        <v>0.501098</v>
+        <v>0.243164</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
@@ -4774,7 +4774,7 @@
         <v>1</v>
       </c>
       <c r="G101" t="n">
-        <v>0.997564</v>
+        <v>0.999936</v>
       </c>
       <c r="H101" t="n">
         <v>1</v>
@@ -4817,7 +4817,7 @@
         <v>1</v>
       </c>
       <c r="G102" t="n">
-        <v>0.999861</v>
+        <v>0.999999</v>
       </c>
       <c r="H102" t="n">
         <v>1</v>
@@ -4860,7 +4860,7 @@
         <v>1</v>
       </c>
       <c r="G103" t="n">
-        <v>0.814649</v>
+        <v>0.678411</v>
       </c>
       <c r="H103" t="n">
         <v>0</v>
@@ -4903,7 +4903,7 @@
         <v>0</v>
       </c>
       <c r="G104" t="n">
-        <v>0.276802</v>
+        <v>0.110224</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -4946,7 +4946,7 @@
         <v>0</v>
       </c>
       <c r="G105" t="n">
-        <v>0.240943</v>
+        <v>0.159346</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -4989,7 +4989,7 @@
         <v>0</v>
       </c>
       <c r="G106" t="n">
-        <v>0.201102</v>
+        <v>0.09488000000000001</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
@@ -5032,7 +5032,7 @@
         <v>0</v>
       </c>
       <c r="G107" t="n">
-        <v>0.21667</v>
+        <v>0.106574</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -5075,7 +5075,7 @@
         <v>1</v>
       </c>
       <c r="G108" t="n">
-        <v>0.998312</v>
+        <v>0.999977</v>
       </c>
       <c r="H108" t="n">
         <v>1</v>
@@ -5118,7 +5118,7 @@
         <v>0</v>
       </c>
       <c r="G109" t="n">
-        <v>0.279618</v>
+        <v>0.145534</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -5161,7 +5161,7 @@
         <v>1</v>
       </c>
       <c r="G110" t="n">
-        <v>0.994306</v>
+        <v>0.999579</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -5204,7 +5204,7 @@
         <v>0</v>
       </c>
       <c r="G111" t="n">
-        <v>0.188992</v>
+        <v>0.09968399999999999</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -5247,7 +5247,7 @@
         <v>0</v>
       </c>
       <c r="G112" t="n">
-        <v>0.2322</v>
+        <v>0.09091</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -5290,7 +5290,7 @@
         <v>0</v>
       </c>
       <c r="G113" t="n">
-        <v>0.265983</v>
+        <v>0.124282</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
@@ -5333,7 +5333,7 @@
         <v>0</v>
       </c>
       <c r="G114" t="n">
-        <v>0.185679</v>
+        <v>0.076989</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -5376,7 +5376,7 @@
         <v>0</v>
       </c>
       <c r="G115" t="n">
-        <v>0.238035</v>
+        <v>0.150592</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
@@ -5419,7 +5419,7 @@
         <v>0</v>
       </c>
       <c r="G116" t="n">
-        <v>0.296292</v>
+        <v>0.139649</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
@@ -5462,7 +5462,7 @@
         <v>1</v>
       </c>
       <c r="G117" t="n">
-        <v>0.644292</v>
+        <v>0.696806</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -5505,7 +5505,7 @@
         <v>0</v>
       </c>
       <c r="G118" t="n">
-        <v>0.230729</v>
+        <v>0.102241</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
@@ -5548,7 +5548,7 @@
         <v>1</v>
       </c>
       <c r="G119" t="n">
-        <v>0.738383</v>
+        <v>0.800944</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
@@ -5591,7 +5591,7 @@
         <v>0</v>
       </c>
       <c r="G120" t="n">
-        <v>0.137202</v>
+        <v>0.06146</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
@@ -5634,7 +5634,7 @@
         <v>1</v>
       </c>
       <c r="G121" t="n">
-        <v>0.650372</v>
+        <v>0.771325</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -5677,7 +5677,7 @@
         <v>1</v>
       </c>
       <c r="G122" t="n">
-        <v>0.7994790000000001</v>
+        <v>0.904558</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
@@ -5720,7 +5720,7 @@
         <v>1</v>
       </c>
       <c r="G123" t="n">
-        <v>0.707059</v>
+        <v>0.643301</v>
       </c>
       <c r="H123" t="n">
         <v>0</v>
@@ -5763,7 +5763,7 @@
         <v>0</v>
       </c>
       <c r="G124" t="n">
-        <v>0.198621</v>
+        <v>0.1039</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -5806,7 +5806,7 @@
         <v>0</v>
       </c>
       <c r="G125" t="n">
-        <v>0.220453</v>
+        <v>0.08802</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
@@ -5849,7 +5849,7 @@
         <v>0</v>
       </c>
       <c r="G126" t="n">
-        <v>0.172813</v>
+        <v>0.111894</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
@@ -5892,7 +5892,7 @@
         <v>0</v>
       </c>
       <c r="G127" t="n">
-        <v>0.14092</v>
+        <v>0.052343</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -5935,7 +5935,7 @@
         <v>0</v>
       </c>
       <c r="G128" t="n">
-        <v>0.186285</v>
+        <v>0.104633</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
         <v>1</v>
       </c>
       <c r="G129" t="n">
-        <v>0.928872</v>
+        <v>0.992194</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -6021,7 +6021,7 @@
         <v>0</v>
       </c>
       <c r="G130" t="n">
-        <v>0.495043</v>
+        <v>0.480789</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -6064,7 +6064,7 @@
         <v>0</v>
       </c>
       <c r="G131" t="n">
-        <v>0.308699</v>
+        <v>0.142554</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
@@ -6107,7 +6107,7 @@
         <v>0</v>
       </c>
       <c r="G132" t="n">
-        <v>0.155215</v>
+        <v>0.107954</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
@@ -6150,7 +6150,7 @@
         <v>0</v>
       </c>
       <c r="G133" t="n">
-        <v>0.242742</v>
+        <v>0.114753</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
@@ -6193,7 +6193,7 @@
         <v>0</v>
       </c>
       <c r="G134" t="n">
-        <v>0.279469</v>
+        <v>0.119586</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -6236,7 +6236,7 @@
         <v>0</v>
       </c>
       <c r="G135" t="n">
-        <v>0.220258</v>
+        <v>0.169505</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -6279,7 +6279,7 @@
         <v>0</v>
       </c>
       <c r="G136" t="n">
-        <v>0.229806</v>
+        <v>0.116815</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -6322,7 +6322,7 @@
         <v>0</v>
       </c>
       <c r="G137" t="n">
-        <v>0.166481</v>
+        <v>0.081665</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
@@ -6365,7 +6365,7 @@
         <v>0</v>
       </c>
       <c r="G138" t="n">
-        <v>0.197143</v>
+        <v>0.08665399999999999</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -6408,7 +6408,7 @@
         <v>0</v>
       </c>
       <c r="G139" t="n">
-        <v>0.242845</v>
+        <v>0.146459</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
@@ -6451,7 +6451,7 @@
         <v>0</v>
       </c>
       <c r="G140" t="n">
-        <v>0.173674</v>
+        <v>0.072453</v>
       </c>
       <c r="H140" t="n">
         <v>0</v>
@@ -6494,7 +6494,7 @@
         <v>0</v>
       </c>
       <c r="G141" t="n">
-        <v>0.332094</v>
+        <v>0.166652</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -6537,7 +6537,7 @@
         <v>0</v>
       </c>
       <c r="G142" t="n">
-        <v>0.286058</v>
+        <v>0.140148</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -6580,7 +6580,7 @@
         <v>0</v>
       </c>
       <c r="G143" t="n">
-        <v>0.264052</v>
+        <v>0.128179</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -6623,7 +6623,7 @@
         <v>0</v>
       </c>
       <c r="G144" t="n">
-        <v>0.346784</v>
+        <v>0.202727</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -6666,7 +6666,7 @@
         <v>0</v>
       </c>
       <c r="G145" t="n">
-        <v>0.235221</v>
+        <v>0.09611599999999999</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -6709,7 +6709,7 @@
         <v>0</v>
       </c>
       <c r="G146" t="n">
-        <v>0.342652</v>
+        <v>0.170555</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
@@ -6752,7 +6752,7 @@
         <v>0</v>
       </c>
       <c r="G147" t="n">
-        <v>0.361242</v>
+        <v>0.24171</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
@@ -6795,7 +6795,7 @@
         <v>0</v>
       </c>
       <c r="G148" t="n">
-        <v>0.242833</v>
+        <v>0.159075</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
@@ -6835,10 +6835,10 @@
         <v>0.022503</v>
       </c>
       <c r="F149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G149" t="n">
-        <v>0.602587</v>
+        <v>0.410655</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
@@ -6881,7 +6881,7 @@
         <v>0</v>
       </c>
       <c r="G150" t="n">
-        <v>0.215054</v>
+        <v>0.153504</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -6924,7 +6924,7 @@
         <v>1</v>
       </c>
       <c r="G151" t="n">
-        <v>0.796725</v>
+        <v>0.8862719999999999</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
@@ -6967,7 +6967,7 @@
         <v>1</v>
       </c>
       <c r="G152" t="n">
-        <v>0.999576</v>
+        <v>0.999995</v>
       </c>
       <c r="H152" t="n">
         <v>1</v>
@@ -7010,7 +7010,7 @@
         <v>0</v>
       </c>
       <c r="G153" t="n">
-        <v>0.374324</v>
+        <v>0.250843</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
@@ -7053,7 +7053,7 @@
         <v>0</v>
       </c>
       <c r="G154" t="n">
-        <v>0.288614</v>
+        <v>0.179252</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -7093,10 +7093,10 @@
         <v>2e-06</v>
       </c>
       <c r="F155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G155" t="n">
-        <v>0.5108239999999999</v>
+        <v>0.206901</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -7139,7 +7139,7 @@
         <v>0</v>
       </c>
       <c r="G156" t="n">
-        <v>0.384609</v>
+        <v>0.23452</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -7182,7 +7182,7 @@
         <v>0</v>
       </c>
       <c r="G157" t="n">
-        <v>0.412015</v>
+        <v>0.38996</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -7225,7 +7225,7 @@
         <v>0</v>
       </c>
       <c r="G158" t="n">
-        <v>0.437471</v>
+        <v>0.231681</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -7268,7 +7268,7 @@
         <v>0</v>
       </c>
       <c r="G159" t="n">
-        <v>0.233973</v>
+        <v>0.08405799999999999</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -7311,7 +7311,7 @@
         <v>0</v>
       </c>
       <c r="G160" t="n">
-        <v>0.21759</v>
+        <v>0.08953800000000001</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -7354,7 +7354,7 @@
         <v>0</v>
       </c>
       <c r="G161" t="n">
-        <v>0.189015</v>
+        <v>0.07881100000000001</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -7397,7 +7397,7 @@
         <v>0</v>
       </c>
       <c r="G162" t="n">
-        <v>0.347034</v>
+        <v>0.258706</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -7437,10 +7437,10 @@
         <v>0</v>
       </c>
       <c r="F163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G163" t="n">
-        <v>0.563368</v>
+        <v>0.313654</v>
       </c>
       <c r="H163" t="n">
         <v>0</v>
@@ -7483,7 +7483,7 @@
         <v>0</v>
       </c>
       <c r="G164" t="n">
-        <v>0.276982</v>
+        <v>0.156406</v>
       </c>
       <c r="H164" t="n">
         <v>0</v>
@@ -7526,7 +7526,7 @@
         <v>0</v>
       </c>
       <c r="G165" t="n">
-        <v>0.218167</v>
+        <v>0.108473</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -7569,7 +7569,7 @@
         <v>1</v>
       </c>
       <c r="G166" t="n">
-        <v>0.556095</v>
+        <v>0.530427</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
@@ -7612,7 +7612,7 @@
         <v>0</v>
       </c>
       <c r="G167" t="n">
-        <v>0.219304</v>
+        <v>0.087538</v>
       </c>
       <c r="H167" t="n">
         <v>0</v>
@@ -7655,7 +7655,7 @@
         <v>0</v>
       </c>
       <c r="G168" t="n">
-        <v>0.334472</v>
+        <v>0.289107</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -7698,7 +7698,7 @@
         <v>0</v>
       </c>
       <c r="G169" t="n">
-        <v>0.297482</v>
+        <v>0.101163</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -7741,7 +7741,7 @@
         <v>0</v>
       </c>
       <c r="G170" t="n">
-        <v>0.206188</v>
+        <v>0.072036</v>
       </c>
       <c r="H170" t="n">
         <v>0</v>
@@ -7784,7 +7784,7 @@
         <v>0</v>
       </c>
       <c r="G171" t="n">
-        <v>0.23248</v>
+        <v>0.101991</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -7827,7 +7827,7 @@
         <v>0</v>
       </c>
       <c r="G172" t="n">
-        <v>0.280911</v>
+        <v>0.165011</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -7870,7 +7870,7 @@
         <v>0</v>
       </c>
       <c r="G173" t="n">
-        <v>0.169421</v>
+        <v>0.041096</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -7913,7 +7913,7 @@
         <v>0</v>
       </c>
       <c r="G174" t="n">
-        <v>0.23051</v>
+        <v>0.068194</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -7956,7 +7956,7 @@
         <v>0</v>
       </c>
       <c r="G175" t="n">
-        <v>0.232996</v>
+        <v>0.108896</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
@@ -7999,7 +7999,7 @@
         <v>0</v>
       </c>
       <c r="G176" t="n">
-        <v>0.313214</v>
+        <v>0.164361</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
         <v>0</v>
       </c>
       <c r="G177" t="n">
-        <v>0.197614</v>
+        <v>0.09575500000000001</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -8085,7 +8085,7 @@
         <v>0</v>
       </c>
       <c r="G178" t="n">
-        <v>0.237606</v>
+        <v>0.116541</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
@@ -8128,7 +8128,7 @@
         <v>0</v>
       </c>
       <c r="G179" t="n">
-        <v>0.187381</v>
+        <v>0.06862</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
@@ -8171,7 +8171,7 @@
         <v>0</v>
       </c>
       <c r="G180" t="n">
-        <v>0.159836</v>
+        <v>0.058558</v>
       </c>
       <c r="H180" t="n">
         <v>0</v>
@@ -8214,7 +8214,7 @@
         <v>0</v>
       </c>
       <c r="G181" t="n">
-        <v>0.345696</v>
+        <v>0.209627</v>
       </c>
       <c r="H181" t="n">
         <v>0</v>
@@ -8257,7 +8257,7 @@
         <v>0</v>
       </c>
       <c r="G182" t="n">
-        <v>0.356487</v>
+        <v>0.261622</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
@@ -8300,7 +8300,7 @@
         <v>0</v>
       </c>
       <c r="G183" t="n">
-        <v>0.210613</v>
+        <v>0.08713899999999999</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -8343,7 +8343,7 @@
         <v>0</v>
       </c>
       <c r="G184" t="n">
-        <v>0.198926</v>
+        <v>0.09360599999999999</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -8386,7 +8386,7 @@
         <v>0</v>
       </c>
       <c r="G185" t="n">
-        <v>0.203347</v>
+        <v>0.06723700000000001</v>
       </c>
       <c r="H185" t="n">
         <v>0</v>
@@ -8429,7 +8429,7 @@
         <v>0</v>
       </c>
       <c r="G186" t="n">
-        <v>0.185508</v>
+        <v>0.068746</v>
       </c>
       <c r="H186" t="n">
         <v>0</v>
@@ -8472,7 +8472,7 @@
         <v>0</v>
       </c>
       <c r="G187" t="n">
-        <v>0.169947</v>
+        <v>0.0725</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -8515,7 +8515,7 @@
         <v>0</v>
       </c>
       <c r="G188" t="n">
-        <v>0.40107</v>
+        <v>0.334314</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
@@ -8558,7 +8558,7 @@
         <v>0</v>
       </c>
       <c r="G189" t="n">
-        <v>0.264289</v>
+        <v>0.125597</v>
       </c>
       <c r="H189" t="n">
         <v>0</v>
@@ -8601,7 +8601,7 @@
         <v>0</v>
       </c>
       <c r="G190" t="n">
-        <v>0.353646</v>
+        <v>0.330692</v>
       </c>
       <c r="H190" t="n">
         <v>0</v>
@@ -8644,7 +8644,7 @@
         <v>0</v>
       </c>
       <c r="G191" t="n">
-        <v>0.343723</v>
+        <v>0.185779</v>
       </c>
       <c r="H191" t="n">
         <v>0</v>
@@ -8687,7 +8687,7 @@
         <v>1</v>
       </c>
       <c r="G192" t="n">
-        <v>0.519487</v>
+        <v>0.698889</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -8727,10 +8727,10 @@
         <v>0.02175</v>
       </c>
       <c r="F193" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G193" t="n">
-        <v>0.591902</v>
+        <v>0.482305</v>
       </c>
       <c r="H193" t="n">
         <v>0</v>
@@ -8773,7 +8773,7 @@
         <v>0</v>
       </c>
       <c r="G194" t="n">
-        <v>0.252422</v>
+        <v>0.105154</v>
       </c>
       <c r="H194" t="n">
         <v>0</v>
@@ -8816,7 +8816,7 @@
         <v>0</v>
       </c>
       <c r="G195" t="n">
-        <v>0.231831</v>
+        <v>0.2201</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
@@ -8859,7 +8859,7 @@
         <v>0</v>
       </c>
       <c r="G196" t="n">
-        <v>0.323646</v>
+        <v>0.120203</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
@@ -8902,7 +8902,7 @@
         <v>1</v>
       </c>
       <c r="G197" t="n">
-        <v>0.81829</v>
+        <v>0.977349</v>
       </c>
       <c r="H197" t="n">
         <v>0</v>
@@ -8945,7 +8945,7 @@
         <v>1</v>
       </c>
       <c r="G198" t="n">
-        <v>0.9779600000000001</v>
+        <v>0.977085</v>
       </c>
       <c r="H198" t="n">
         <v>0</v>
@@ -8988,7 +8988,7 @@
         <v>1</v>
       </c>
       <c r="G199" t="n">
-        <v>0.779961</v>
+        <v>0.729089</v>
       </c>
       <c r="H199" t="n">
         <v>0</v>
@@ -9031,7 +9031,7 @@
         <v>0</v>
       </c>
       <c r="G200" t="n">
-        <v>0.484101</v>
+        <v>0.359185</v>
       </c>
       <c r="H200" t="n">
         <v>0</v>
@@ -9074,7 +9074,7 @@
         <v>0</v>
       </c>
       <c r="G201" t="n">
-        <v>0.235763</v>
+        <v>0.197036</v>
       </c>
       <c r="H201" t="n">
         <v>0</v>
@@ -9117,7 +9117,7 @@
         <v>0</v>
       </c>
       <c r="G202" t="n">
-        <v>0.09696299999999999</v>
+        <v>0.08126800000000001</v>
       </c>
       <c r="H202" t="n">
         <v>0</v>
@@ -9160,7 +9160,7 @@
         <v>1</v>
       </c>
       <c r="G203" t="n">
-        <v>0.6914</v>
+        <v>0.715039</v>
       </c>
       <c r="H203" t="n">
         <v>0</v>
@@ -9203,7 +9203,7 @@
         <v>0</v>
       </c>
       <c r="G204" t="n">
-        <v>0.287716</v>
+        <v>0.295364</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
@@ -9246,7 +9246,7 @@
         <v>0</v>
       </c>
       <c r="G205" t="n">
-        <v>0.145991</v>
+        <v>0.068242</v>
       </c>
       <c r="H205" t="n">
         <v>0</v>
@@ -9289,7 +9289,7 @@
         <v>1</v>
       </c>
       <c r="G206" t="n">
-        <v>0.706356</v>
+        <v>0.735317</v>
       </c>
       <c r="H206" t="n">
         <v>0</v>
@@ -9332,7 +9332,7 @@
         <v>0</v>
       </c>
       <c r="G207" t="n">
-        <v>0.426562</v>
+        <v>0.260147</v>
       </c>
       <c r="H207" t="n">
         <v>0</v>
@@ -9375,7 +9375,7 @@
         <v>0</v>
       </c>
       <c r="G208" t="n">
-        <v>0.303512</v>
+        <v>0.229172</v>
       </c>
       <c r="H208" t="n">
         <v>0</v>
@@ -9418,7 +9418,7 @@
         <v>0</v>
       </c>
       <c r="G209" t="n">
-        <v>0.245976</v>
+        <v>0.207281</v>
       </c>
       <c r="H209" t="n">
         <v>0</v>
@@ -9461,7 +9461,7 @@
         <v>1</v>
       </c>
       <c r="G210" t="n">
-        <v>0.9140779999999999</v>
+        <v>0.96774</v>
       </c>
       <c r="H210" t="n">
         <v>1</v>
@@ -9504,7 +9504,7 @@
         <v>0</v>
       </c>
       <c r="G211" t="n">
-        <v>0.154918</v>
+        <v>0.070372</v>
       </c>
       <c r="H211" t="n">
         <v>0</v>
@@ -9547,7 +9547,7 @@
         <v>0</v>
       </c>
       <c r="G212" t="n">
-        <v>0.226102</v>
+        <v>0.10308</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
@@ -9590,7 +9590,7 @@
         <v>0</v>
       </c>
       <c r="G213" t="n">
-        <v>0.237153</v>
+        <v>0.130786</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -9633,7 +9633,7 @@
         <v>0</v>
       </c>
       <c r="G214" t="n">
-        <v>0.277535</v>
+        <v>0.119256</v>
       </c>
       <c r="H214" t="n">
         <v>0</v>
@@ -9676,7 +9676,7 @@
         <v>0</v>
       </c>
       <c r="G215" t="n">
-        <v>0.198434</v>
+        <v>0.09088499999999999</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -9719,7 +9719,7 @@
         <v>0</v>
       </c>
       <c r="G216" t="n">
-        <v>0.459606</v>
+        <v>0.483563</v>
       </c>
       <c r="H216" t="n">
         <v>0</v>
@@ -9762,7 +9762,7 @@
         <v>0</v>
       </c>
       <c r="G217" t="n">
-        <v>0.18839</v>
+        <v>0.101166</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
@@ -9805,7 +9805,7 @@
         <v>0</v>
       </c>
       <c r="G218" t="n">
-        <v>0.406736</v>
+        <v>0.333731</v>
       </c>
       <c r="H218" t="n">
         <v>0</v>
@@ -9848,7 +9848,7 @@
         <v>0</v>
       </c>
       <c r="G219" t="n">
-        <v>0.201184</v>
+        <v>0.096466</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -9891,7 +9891,7 @@
         <v>0</v>
       </c>
       <c r="G220" t="n">
-        <v>0.210863</v>
+        <v>0.127837</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -9934,7 +9934,7 @@
         <v>0</v>
       </c>
       <c r="G221" t="n">
-        <v>0.349098</v>
+        <v>0.249423</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
@@ -9977,7 +9977,7 @@
         <v>1</v>
       </c>
       <c r="G222" t="n">
-        <v>0.5541160000000001</v>
+        <v>0.61849</v>
       </c>
       <c r="H222" t="n">
         <v>0</v>
@@ -10020,7 +10020,7 @@
         <v>0</v>
       </c>
       <c r="G223" t="n">
-        <v>0.342028</v>
+        <v>0.35745</v>
       </c>
       <c r="H223" t="n">
         <v>0</v>
@@ -10063,7 +10063,7 @@
         <v>0</v>
       </c>
       <c r="G224" t="n">
-        <v>0.175945</v>
+        <v>0.11773</v>
       </c>
       <c r="H224" t="n">
         <v>0</v>
@@ -10106,7 +10106,7 @@
         <v>0</v>
       </c>
       <c r="G225" t="n">
-        <v>0.347202</v>
+        <v>0.268926</v>
       </c>
       <c r="H225" t="n">
         <v>0</v>
@@ -10149,7 +10149,7 @@
         <v>0</v>
       </c>
       <c r="G226" t="n">
-        <v>0.159665</v>
+        <v>0.073841</v>
       </c>
       <c r="H226" t="n">
         <v>0</v>
@@ -10192,7 +10192,7 @@
         <v>0</v>
       </c>
       <c r="G227" t="n">
-        <v>0.368889</v>
+        <v>0.319463</v>
       </c>
       <c r="H227" t="n">
         <v>0</v>
@@ -10235,7 +10235,7 @@
         <v>0</v>
       </c>
       <c r="G228" t="n">
-        <v>0.217763</v>
+        <v>0.147276</v>
       </c>
       <c r="H228" t="n">
         <v>0</v>
@@ -10278,7 +10278,7 @@
         <v>0</v>
       </c>
       <c r="G229" t="n">
-        <v>0.206262</v>
+        <v>0.133121</v>
       </c>
       <c r="H229" t="n">
         <v>0</v>
@@ -10321,7 +10321,7 @@
         <v>0</v>
       </c>
       <c r="G230" t="n">
-        <v>0.199614</v>
+        <v>0.12036</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -10364,7 +10364,7 @@
         <v>1</v>
       </c>
       <c r="G231" t="n">
-        <v>0.75679</v>
+        <v>0.874337</v>
       </c>
       <c r="H231" t="n">
         <v>0</v>
@@ -10407,7 +10407,7 @@
         <v>0</v>
       </c>
       <c r="G232" t="n">
-        <v>0.317642</v>
+        <v>0.293476</v>
       </c>
       <c r="H232" t="n">
         <v>1</v>
@@ -10450,7 +10450,7 @@
         <v>1</v>
       </c>
       <c r="G233" t="n">
-        <v>0.995954</v>
+        <v>0.999379</v>
       </c>
       <c r="H233" t="n">
         <v>0</v>
@@ -10493,7 +10493,7 @@
         <v>0</v>
       </c>
       <c r="G234" t="n">
-        <v>0.388278</v>
+        <v>0.19293</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -10533,10 +10533,10 @@
         <v>0.004121</v>
       </c>
       <c r="F235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G235" t="n">
-        <v>0.491823</v>
+        <v>0.539623</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -10579,7 +10579,7 @@
         <v>0</v>
       </c>
       <c r="G236" t="n">
-        <v>0.133058</v>
+        <v>0.106173</v>
       </c>
       <c r="H236" t="n">
         <v>0</v>
@@ -10622,7 +10622,7 @@
         <v>0</v>
       </c>
       <c r="G237" t="n">
-        <v>0.154683</v>
+        <v>0.07641100000000001</v>
       </c>
       <c r="H237" t="n">
         <v>0</v>
@@ -10665,7 +10665,7 @@
         <v>0</v>
       </c>
       <c r="G238" t="n">
-        <v>0.156282</v>
+        <v>0.066818</v>
       </c>
       <c r="H238" t="n">
         <v>0</v>
@@ -10708,7 +10708,7 @@
         <v>0</v>
       </c>
       <c r="G239" t="n">
-        <v>0.161355</v>
+        <v>0.07111000000000001</v>
       </c>
       <c r="H239" t="n">
         <v>0</v>
@@ -10751,7 +10751,7 @@
         <v>0</v>
       </c>
       <c r="G240" t="n">
-        <v>0.177387</v>
+        <v>0.065749</v>
       </c>
       <c r="H240" t="n">
         <v>0</v>
@@ -10794,7 +10794,7 @@
         <v>0</v>
       </c>
       <c r="G241" t="n">
-        <v>0.167397</v>
+        <v>0.092747</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -10837,7 +10837,7 @@
         <v>0</v>
       </c>
       <c r="G242" t="n">
-        <v>0.144592</v>
+        <v>0.0571</v>
       </c>
       <c r="H242" t="n">
         <v>0</v>
@@ -10880,7 +10880,7 @@
         <v>0</v>
       </c>
       <c r="G243" t="n">
-        <v>0.258359</v>
+        <v>0.191746</v>
       </c>
       <c r="H243" t="n">
         <v>0</v>
@@ -10923,7 +10923,7 @@
         <v>0</v>
       </c>
       <c r="G244" t="n">
-        <v>0.286043</v>
+        <v>0.218898</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -10966,7 +10966,7 @@
         <v>1</v>
       </c>
       <c r="G245" t="n">
-        <v>0.670254</v>
+        <v>0.618833</v>
       </c>
       <c r="H245" t="n">
         <v>0</v>
@@ -11009,7 +11009,7 @@
         <v>1</v>
       </c>
       <c r="G246" t="n">
-        <v>0.944316</v>
+        <v>0.9810179999999999</v>
       </c>
       <c r="H246" t="n">
         <v>0</v>
@@ -11052,7 +11052,7 @@
         <v>1</v>
       </c>
       <c r="G247" t="n">
-        <v>0.955063</v>
+        <v>0.990556</v>
       </c>
       <c r="H247" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
         <v>0</v>
       </c>
       <c r="G248" t="n">
-        <v>0.407818</v>
+        <v>0.38449</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -11138,7 +11138,7 @@
         <v>1</v>
       </c>
       <c r="G249" t="n">
-        <v>0.982002</v>
+        <v>0.995705</v>
       </c>
       <c r="H249" t="n">
         <v>0</v>
@@ -11181,7 +11181,7 @@
         <v>0</v>
       </c>
       <c r="G250" t="n">
-        <v>0.267168</v>
+        <v>0.161093</v>
       </c>
       <c r="H250" t="n">
         <v>0</v>
@@ -11224,7 +11224,7 @@
         <v>0</v>
       </c>
       <c r="G251" t="n">
-        <v>0.226307</v>
+        <v>0.092719</v>
       </c>
       <c r="H251" t="n">
         <v>0</v>
@@ -11267,7 +11267,7 @@
         <v>1</v>
       </c>
       <c r="G252" t="n">
-        <v>0.670081</v>
+        <v>0.726833</v>
       </c>
       <c r="H252" t="n">
         <v>0</v>
@@ -11310,7 +11310,7 @@
         <v>0</v>
       </c>
       <c r="G253" t="n">
-        <v>0.173356</v>
+        <v>0.118034</v>
       </c>
       <c r="H253" t="n">
         <v>0</v>
@@ -11353,7 +11353,7 @@
         <v>0</v>
       </c>
       <c r="G254" t="n">
-        <v>0.264362</v>
+        <v>0.23415</v>
       </c>
       <c r="H254" t="n">
         <v>0</v>
@@ -11396,7 +11396,7 @@
         <v>0</v>
       </c>
       <c r="G255" t="n">
-        <v>0.394118</v>
+        <v>0.321816</v>
       </c>
       <c r="H255" t="n">
         <v>0</v>
@@ -11439,7 +11439,7 @@
         <v>1</v>
       </c>
       <c r="G256" t="n">
-        <v>0.969125</v>
+        <v>0.987886</v>
       </c>
       <c r="H256" t="n">
         <v>1</v>
@@ -11482,7 +11482,7 @@
         <v>1</v>
       </c>
       <c r="G257" t="n">
-        <v>0.958493</v>
+        <v>0.9798750000000001</v>
       </c>
       <c r="H257" t="n">
         <v>1</v>
@@ -11525,7 +11525,7 @@
         <v>1</v>
       </c>
       <c r="G258" t="n">
-        <v>0.95867</v>
+        <v>0.9810140000000001</v>
       </c>
       <c r="H258" t="n">
         <v>0</v>
@@ -11568,7 +11568,7 @@
         <v>1</v>
       </c>
       <c r="G259" t="n">
-        <v>0.879179</v>
+        <v>0.93724</v>
       </c>
       <c r="H259" t="n">
         <v>1</v>
@@ -11611,7 +11611,7 @@
         <v>0</v>
       </c>
       <c r="G260" t="n">
-        <v>0.186508</v>
+        <v>0.105227</v>
       </c>
       <c r="H260" t="n">
         <v>0</v>
@@ -11654,7 +11654,7 @@
         <v>1</v>
       </c>
       <c r="G261" t="n">
-        <v>0.611445</v>
+        <v>0.716363</v>
       </c>
       <c r="H261" t="n">
         <v>0</v>
@@ -11694,10 +11694,10 @@
         <v>0.494367</v>
       </c>
       <c r="F262" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G262" t="n">
-        <v>0.561075</v>
+        <v>0.474494</v>
       </c>
       <c r="H262" t="n">
         <v>0</v>
@@ -11740,7 +11740,7 @@
         <v>0</v>
       </c>
       <c r="G263" t="n">
-        <v>0.172512</v>
+        <v>0.077894</v>
       </c>
       <c r="H263" t="n">
         <v>0</v>
@@ -11783,7 +11783,7 @@
         <v>1</v>
       </c>
       <c r="G264" t="n">
-        <v>0.986905</v>
+        <v>0.997023</v>
       </c>
       <c r="H264" t="n">
         <v>0</v>
@@ -11826,7 +11826,7 @@
         <v>0</v>
       </c>
       <c r="G265" t="n">
-        <v>0.170396</v>
+        <v>0.110638</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -11869,7 +11869,7 @@
         <v>0</v>
       </c>
       <c r="G266" t="n">
-        <v>0.176018</v>
+        <v>0.088349</v>
       </c>
       <c r="H266" t="n">
         <v>0</v>
@@ -11912,7 +11912,7 @@
         <v>1</v>
       </c>
       <c r="G267" t="n">
-        <v>0.953361</v>
+        <v>0.974093</v>
       </c>
       <c r="H267" t="n">
         <v>0</v>
@@ -11955,7 +11955,7 @@
         <v>1</v>
       </c>
       <c r="G268" t="n">
-        <v>0.979181</v>
+        <v>0.998242</v>
       </c>
       <c r="H268" t="n">
         <v>0</v>
@@ -11998,7 +11998,7 @@
         <v>0</v>
       </c>
       <c r="G269" t="n">
-        <v>0.219998</v>
+        <v>0.105513</v>
       </c>
       <c r="H269" t="n">
         <v>0</v>
@@ -12041,7 +12041,7 @@
         <v>0</v>
       </c>
       <c r="G270" t="n">
-        <v>0.251155</v>
+        <v>0.158955</v>
       </c>
       <c r="H270" t="n">
         <v>0</v>
@@ -12084,7 +12084,7 @@
         <v>0</v>
       </c>
       <c r="G271" t="n">
-        <v>0.162263</v>
+        <v>0.080993</v>
       </c>
       <c r="H271" t="n">
         <v>0</v>
@@ -12127,7 +12127,7 @@
         <v>0</v>
       </c>
       <c r="G272" t="n">
-        <v>0.297946</v>
+        <v>0.260147</v>
       </c>
       <c r="H272" t="n">
         <v>0</v>
@@ -12170,7 +12170,7 @@
         <v>1</v>
       </c>
       <c r="G273" t="n">
-        <v>0.6893860000000001</v>
+        <v>0.6691820000000001</v>
       </c>
       <c r="H273" t="n">
         <v>0</v>
@@ -12213,7 +12213,7 @@
         <v>1</v>
       </c>
       <c r="G274" t="n">
-        <v>0.692764</v>
+        <v>0.53977</v>
       </c>
       <c r="H274" t="n">
         <v>0</v>
@@ -12253,10 +12253,10 @@
         <v>8.8e-05</v>
       </c>
       <c r="F275" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G275" t="n">
-        <v>0.5588070000000001</v>
+        <v>0.33583</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>
@@ -12299,7 +12299,7 @@
         <v>1</v>
       </c>
       <c r="G276" t="n">
-        <v>0.671389</v>
+        <v>0.701724</v>
       </c>
       <c r="H276" t="n">
         <v>0</v>
@@ -12342,7 +12342,7 @@
         <v>0</v>
       </c>
       <c r="G277" t="n">
-        <v>0.423798</v>
+        <v>0.462</v>
       </c>
       <c r="H277" t="n">
         <v>0</v>
@@ -12385,7 +12385,7 @@
         <v>0</v>
       </c>
       <c r="G278" t="n">
-        <v>0.298063</v>
+        <v>0.252504</v>
       </c>
       <c r="H278" t="n">
         <v>0</v>
@@ -12428,7 +12428,7 @@
         <v>0</v>
       </c>
       <c r="G279" t="n">
-        <v>0.198166</v>
+        <v>0.09909800000000001</v>
       </c>
       <c r="H279" t="n">
         <v>0</v>
@@ -12471,7 +12471,7 @@
         <v>0</v>
       </c>
       <c r="G280" t="n">
-        <v>0.168562</v>
+        <v>0.108039</v>
       </c>
       <c r="H280" t="n">
         <v>0</v>
@@ -12514,7 +12514,7 @@
         <v>0</v>
       </c>
       <c r="G281" t="n">
-        <v>0.294854</v>
+        <v>0.229264</v>
       </c>
       <c r="H281" t="n">
         <v>0</v>
@@ -12557,7 +12557,7 @@
         <v>0</v>
       </c>
       <c r="G282" t="n">
-        <v>0.130777</v>
+        <v>0.06829499999999999</v>
       </c>
       <c r="H282" t="n">
         <v>0</v>
@@ -12600,7 +12600,7 @@
         <v>0</v>
       </c>
       <c r="G283" t="n">
-        <v>0.173542</v>
+        <v>0.137994</v>
       </c>
       <c r="H283" t="n">
         <v>0</v>
@@ -12643,7 +12643,7 @@
         <v>0</v>
       </c>
       <c r="G284" t="n">
-        <v>0.117639</v>
+        <v>0.083063</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -12686,7 +12686,7 @@
         <v>0</v>
       </c>
       <c r="G285" t="n">
-        <v>0.282853</v>
+        <v>0.138114</v>
       </c>
       <c r="H285" t="n">
         <v>0</v>
@@ -12726,10 +12726,10 @@
         <v>2e-06</v>
       </c>
       <c r="F286" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G286" t="n">
-        <v>0.572215</v>
+        <v>0.409809</v>
       </c>
       <c r="H286" t="n">
         <v>0</v>
@@ -12772,7 +12772,7 @@
         <v>1</v>
       </c>
       <c r="G287" t="n">
-        <v>0.854091</v>
+        <v>0.7639550000000001</v>
       </c>
       <c r="H287" t="n">
         <v>0</v>
@@ -12815,7 +12815,7 @@
         <v>0</v>
       </c>
       <c r="G288" t="n">
-        <v>0.387023</v>
+        <v>0.320869</v>
       </c>
       <c r="H288" t="n">
         <v>0</v>
@@ -12858,7 +12858,7 @@
         <v>0</v>
       </c>
       <c r="G289" t="n">
-        <v>0.244867</v>
+        <v>0.163668</v>
       </c>
       <c r="H289" t="n">
         <v>0</v>
@@ -12901,7 +12901,7 @@
         <v>0</v>
       </c>
       <c r="G290" t="n">
-        <v>0.322103</v>
+        <v>0.20297</v>
       </c>
       <c r="H290" t="n">
         <v>0</v>
@@ -12944,7 +12944,7 @@
         <v>0</v>
       </c>
       <c r="G291" t="n">
-        <v>0.439571</v>
+        <v>0.240464</v>
       </c>
       <c r="H291" t="n">
         <v>0</v>
@@ -12987,7 +12987,7 @@
         <v>0</v>
       </c>
       <c r="G292" t="n">
-        <v>0.290152</v>
+        <v>0.328051</v>
       </c>
       <c r="H292" t="n">
         <v>0</v>
@@ -13030,7 +13030,7 @@
         <v>0</v>
       </c>
       <c r="G293" t="n">
-        <v>0.269973</v>
+        <v>0.219831</v>
       </c>
       <c r="H293" t="n">
         <v>0</v>
@@ -13073,7 +13073,7 @@
         <v>0</v>
       </c>
       <c r="G294" t="n">
-        <v>0.071422</v>
+        <v>0.074702</v>
       </c>
       <c r="H294" t="n">
         <v>0</v>
@@ -13116,7 +13116,7 @@
         <v>0</v>
       </c>
       <c r="G295" t="n">
-        <v>0.159834</v>
+        <v>0.07172099999999999</v>
       </c>
       <c r="H295" t="n">
         <v>0</v>
@@ -13159,7 +13159,7 @@
         <v>1</v>
       </c>
       <c r="G296" t="n">
-        <v>0.998068</v>
+        <v>0.999638</v>
       </c>
       <c r="H296" t="n">
         <v>1</v>
@@ -13202,7 +13202,7 @@
         <v>1</v>
       </c>
       <c r="G297" t="n">
-        <v>0.649215</v>
+        <v>0.590774</v>
       </c>
       <c r="H297" t="n">
         <v>0</v>
@@ -13245,7 +13245,7 @@
         <v>0</v>
       </c>
       <c r="G298" t="n">
-        <v>0.357481</v>
+        <v>0.23962</v>
       </c>
       <c r="H298" t="n">
         <v>0</v>
@@ -13288,7 +13288,7 @@
         <v>0</v>
       </c>
       <c r="G299" t="n">
-        <v>0.47597</v>
+        <v>0.34538</v>
       </c>
       <c r="H299" t="n">
         <v>0</v>
@@ -13331,7 +13331,7 @@
         <v>0</v>
       </c>
       <c r="G300" t="n">
-        <v>0.353237</v>
+        <v>0.352133</v>
       </c>
       <c r="H300" t="n">
         <v>0</v>
@@ -13374,7 +13374,7 @@
         <v>0</v>
       </c>
       <c r="G301" t="n">
-        <v>0.159296</v>
+        <v>0.109211</v>
       </c>
       <c r="H301" t="n">
         <v>0</v>
@@ -13417,7 +13417,7 @@
         <v>0</v>
       </c>
       <c r="G302" t="n">
-        <v>0.255334</v>
+        <v>0.212044</v>
       </c>
       <c r="H302" t="n">
         <v>0</v>
@@ -13460,7 +13460,7 @@
         <v>1</v>
       </c>
       <c r="G303" t="n">
-        <v>0.936877</v>
+        <v>0.977172</v>
       </c>
       <c r="H303" t="n">
         <v>1</v>
@@ -13503,7 +13503,7 @@
         <v>1</v>
       </c>
       <c r="G304" t="n">
-        <v>0.978135</v>
+        <v>0.996126</v>
       </c>
       <c r="H304" t="n">
         <v>1</v>
@@ -13546,7 +13546,7 @@
         <v>0</v>
       </c>
       <c r="G305" t="n">
-        <v>0.095792</v>
+        <v>0.076192</v>
       </c>
       <c r="H305" t="n">
         <v>0</v>
@@ -13589,7 +13589,7 @@
         <v>0</v>
       </c>
       <c r="G306" t="n">
-        <v>0.265261</v>
+        <v>0.199472</v>
       </c>
       <c r="H306" t="n">
         <v>1</v>
@@ -13632,7 +13632,7 @@
         <v>0</v>
       </c>
       <c r="G307" t="n">
-        <v>0.189866</v>
+        <v>0.160814</v>
       </c>
       <c r="H307" t="n">
         <v>0</v>
@@ -13675,7 +13675,7 @@
         <v>0</v>
       </c>
       <c r="G308" t="n">
-        <v>0.205033</v>
+        <v>0.119314</v>
       </c>
       <c r="H308" t="n">
         <v>0</v>
@@ -13718,7 +13718,7 @@
         <v>1</v>
       </c>
       <c r="G309" t="n">
-        <v>0.624668</v>
+        <v>0.7254429999999999</v>
       </c>
       <c r="H309" t="n">
         <v>0</v>
@@ -13761,7 +13761,7 @@
         <v>0</v>
       </c>
       <c r="G310" t="n">
-        <v>0.106096</v>
+        <v>0.064717</v>
       </c>
       <c r="H310" t="n">
         <v>0</v>
@@ -13804,7 +13804,7 @@
         <v>0</v>
       </c>
       <c r="G311" t="n">
-        <v>0.226764</v>
+        <v>0.17037</v>
       </c>
       <c r="H311" t="n">
         <v>0</v>
@@ -13847,7 +13847,7 @@
         <v>0</v>
       </c>
       <c r="G312" t="n">
-        <v>0.165666</v>
+        <v>0.117489</v>
       </c>
       <c r="H312" t="n">
         <v>0</v>
@@ -13890,7 +13890,7 @@
         <v>0</v>
       </c>
       <c r="G313" t="n">
-        <v>0.254579</v>
+        <v>0.191531</v>
       </c>
       <c r="H313" t="n">
         <v>0</v>
@@ -13933,7 +13933,7 @@
         <v>0</v>
       </c>
       <c r="G314" t="n">
-        <v>0.08656700000000001</v>
+        <v>0.090779</v>
       </c>
       <c r="H314" t="n">
         <v>0</v>
@@ -13976,7 +13976,7 @@
         <v>0</v>
       </c>
       <c r="G315" t="n">
-        <v>0.141117</v>
+        <v>0.077112</v>
       </c>
       <c r="H315" t="n">
         <v>0</v>
@@ -14019,7 +14019,7 @@
         <v>0</v>
       </c>
       <c r="G316" t="n">
-        <v>0.361327</v>
+        <v>0.317768</v>
       </c>
       <c r="H316" t="n">
         <v>0</v>
@@ -14062,7 +14062,7 @@
         <v>0</v>
       </c>
       <c r="G317" t="n">
-        <v>0.08780300000000001</v>
+        <v>0.064621</v>
       </c>
       <c r="H317" t="n">
         <v>0</v>
@@ -14102,10 +14102,10 @@
         <v>0.006998</v>
       </c>
       <c r="F318" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G318" t="n">
-        <v>0.5918639999999999</v>
+        <v>0.297117</v>
       </c>
       <c r="H318" t="n">
         <v>0</v>
@@ -14148,7 +14148,7 @@
         <v>0</v>
       </c>
       <c r="G319" t="n">
-        <v>0.36662</v>
+        <v>0.382583</v>
       </c>
       <c r="H319" t="n">
         <v>0</v>
@@ -14191,7 +14191,7 @@
         <v>1</v>
       </c>
       <c r="G320" t="n">
-        <v>0.929347</v>
+        <v>0.875776</v>
       </c>
       <c r="H320" t="n">
         <v>1</v>
@@ -14234,7 +14234,7 @@
         <v>0</v>
       </c>
       <c r="G321" t="n">
-        <v>0.141958</v>
+        <v>0.09400699999999999</v>
       </c>
       <c r="H321" t="n">
         <v>0</v>
@@ -14277,7 +14277,7 @@
         <v>0</v>
       </c>
       <c r="G322" t="n">
-        <v>0.128271</v>
+        <v>0.141078</v>
       </c>
       <c r="H322" t="n">
         <v>0</v>
@@ -14320,7 +14320,7 @@
         <v>0</v>
       </c>
       <c r="G323" t="n">
-        <v>0.147166</v>
+        <v>0.08939900000000001</v>
       </c>
       <c r="H323" t="n">
         <v>0</v>
@@ -14363,7 +14363,7 @@
         <v>0</v>
       </c>
       <c r="G324" t="n">
-        <v>0.118588</v>
+        <v>0.138278</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -14406,7 +14406,7 @@
         <v>0</v>
       </c>
       <c r="G325" t="n">
-        <v>0.089957</v>
+        <v>0.06351</v>
       </c>
       <c r="H325" t="n">
         <v>0</v>
@@ -14449,7 +14449,7 @@
         <v>0</v>
       </c>
       <c r="G326" t="n">
-        <v>0.133294</v>
+        <v>0.094194</v>
       </c>
       <c r="H326" t="n">
         <v>0</v>
@@ -14492,7 +14492,7 @@
         <v>0</v>
       </c>
       <c r="G327" t="n">
-        <v>0.274354</v>
+        <v>0.2232</v>
       </c>
       <c r="H327" t="n">
         <v>0</v>
@@ -14535,7 +14535,7 @@
         <v>1</v>
       </c>
       <c r="G328" t="n">
-        <v>0.881412</v>
+        <v>0.913386</v>
       </c>
       <c r="H328" t="n">
         <v>0</v>
@@ -14578,7 +14578,7 @@
         <v>0</v>
       </c>
       <c r="G329" t="n">
-        <v>0.207869</v>
+        <v>0.090101</v>
       </c>
       <c r="H329" t="n">
         <v>0</v>
@@ -14621,7 +14621,7 @@
         <v>0</v>
       </c>
       <c r="G330" t="n">
-        <v>0.104537</v>
+        <v>0.07195799999999999</v>
       </c>
       <c r="H330" t="n">
         <v>0</v>
@@ -14664,7 +14664,7 @@
         <v>1</v>
       </c>
       <c r="G331" t="n">
-        <v>0.941106</v>
+        <v>0.975563</v>
       </c>
       <c r="H331" t="n">
         <v>0</v>
@@ -14707,7 +14707,7 @@
         <v>0</v>
       </c>
       <c r="G332" t="n">
-        <v>0.12274</v>
+        <v>0.057568</v>
       </c>
       <c r="H332" t="n">
         <v>0</v>
@@ -14750,7 +14750,7 @@
         <v>1</v>
       </c>
       <c r="G333" t="n">
-        <v>0.988228</v>
+        <v>0.996799</v>
       </c>
       <c r="H333" t="n">
         <v>0</v>
@@ -14793,7 +14793,7 @@
         <v>0</v>
       </c>
       <c r="G334" t="n">
-        <v>0.242269</v>
+        <v>0.250739</v>
       </c>
       <c r="H334" t="n">
         <v>0</v>
@@ -14836,7 +14836,7 @@
         <v>0</v>
       </c>
       <c r="G335" t="n">
-        <v>0.171492</v>
+        <v>0.14896</v>
       </c>
       <c r="H335" t="n">
         <v>0</v>
@@ -14879,7 +14879,7 @@
         <v>0</v>
       </c>
       <c r="G336" t="n">
-        <v>0.230977</v>
+        <v>0.140587</v>
       </c>
       <c r="H336" t="n">
         <v>0</v>
@@ -14922,7 +14922,7 @@
         <v>0</v>
       </c>
       <c r="G337" t="n">
-        <v>0.089208</v>
+        <v>0.059686</v>
       </c>
       <c r="H337" t="n">
         <v>0</v>
@@ -14965,7 +14965,7 @@
         <v>0</v>
       </c>
       <c r="G338" t="n">
-        <v>0.132456</v>
+        <v>0.073224</v>
       </c>
       <c r="H338" t="n">
         <v>0</v>
@@ -15008,7 +15008,7 @@
         <v>0</v>
       </c>
       <c r="G339" t="n">
-        <v>0.078134</v>
+        <v>0.064037</v>
       </c>
       <c r="H339" t="n">
         <v>0</v>
@@ -15051,7 +15051,7 @@
         <v>0</v>
       </c>
       <c r="G340" t="n">
-        <v>0.141188</v>
+        <v>0.124948</v>
       </c>
       <c r="H340" t="n">
         <v>0</v>
@@ -15094,7 +15094,7 @@
         <v>0</v>
       </c>
       <c r="G341" t="n">
-        <v>0.181312</v>
+        <v>0.111354</v>
       </c>
       <c r="H341" t="n">
         <v>0</v>
@@ -15137,7 +15137,7 @@
         <v>0</v>
       </c>
       <c r="G342" t="n">
-        <v>0.064258</v>
+        <v>0.059695</v>
       </c>
       <c r="H342" t="n">
         <v>0</v>
@@ -15180,7 +15180,7 @@
         <v>0</v>
       </c>
       <c r="G343" t="n">
-        <v>0.08835999999999999</v>
+        <v>0.076041</v>
       </c>
       <c r="H343" t="n">
         <v>0</v>
@@ -15223,7 +15223,7 @@
         <v>0</v>
       </c>
       <c r="G344" t="n">
-        <v>0.043356</v>
+        <v>0.044591</v>
       </c>
       <c r="H344" t="n">
         <v>0</v>
@@ -15266,7 +15266,7 @@
         <v>0</v>
       </c>
       <c r="G345" t="n">
-        <v>0.229061</v>
+        <v>0.151972</v>
       </c>
       <c r="H345" t="n">
         <v>0</v>
@@ -15309,7 +15309,7 @@
         <v>0</v>
       </c>
       <c r="G346" t="n">
-        <v>0.307826</v>
+        <v>0.171712</v>
       </c>
       <c r="H346" t="n">
         <v>0</v>
@@ -15352,7 +15352,7 @@
         <v>0</v>
       </c>
       <c r="G347" t="n">
-        <v>0.388876</v>
+        <v>0.23799</v>
       </c>
       <c r="H347" t="n">
         <v>0</v>
@@ -15392,10 +15392,10 @@
         <v>0.0061</v>
       </c>
       <c r="F348" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G348" t="n">
-        <v>0.513384</v>
+        <v>0.239704</v>
       </c>
       <c r="H348" t="n">
         <v>0</v>
@@ -15438,7 +15438,7 @@
         <v>0</v>
       </c>
       <c r="G349" t="n">
-        <v>0.444534</v>
+        <v>0.437213</v>
       </c>
       <c r="H349" t="n">
         <v>0</v>
@@ -15481,7 +15481,7 @@
         <v>1</v>
       </c>
       <c r="G350" t="n">
-        <v>0.7695340000000001</v>
+        <v>0.7138600000000001</v>
       </c>
       <c r="H350" t="n">
         <v>0</v>
@@ -15521,10 +15521,10 @@
         <v>0.171477</v>
       </c>
       <c r="F351" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G351" t="n">
-        <v>0.6034040000000001</v>
+        <v>0.407491</v>
       </c>
       <c r="H351" t="n">
         <v>0</v>
@@ -15567,7 +15567,7 @@
         <v>0</v>
       </c>
       <c r="G352" t="n">
-        <v>0.197671</v>
+        <v>0.09893299999999999</v>
       </c>
       <c r="H352" t="n">
         <v>0</v>
@@ -15610,7 +15610,7 @@
         <v>0</v>
       </c>
       <c r="G353" t="n">
-        <v>0.119772</v>
+        <v>0.104316</v>
       </c>
       <c r="H353" t="n">
         <v>0</v>
@@ -15653,7 +15653,7 @@
         <v>0</v>
       </c>
       <c r="G354" t="n">
-        <v>0.14549</v>
+        <v>0.128369</v>
       </c>
       <c r="H354" t="n">
         <v>0</v>
@@ -15696,7 +15696,7 @@
         <v>0</v>
       </c>
       <c r="G355" t="n">
-        <v>0.08579000000000001</v>
+        <v>0.044864</v>
       </c>
       <c r="H355" t="n">
         <v>0</v>
@@ -15739,7 +15739,7 @@
         <v>0</v>
       </c>
       <c r="G356" t="n">
-        <v>0.060042</v>
+        <v>0.048538</v>
       </c>
       <c r="H356" t="n">
         <v>0</v>
@@ -15782,7 +15782,7 @@
         <v>0</v>
       </c>
       <c r="G357" t="n">
-        <v>0.079738</v>
+        <v>0.07983800000000001</v>
       </c>
       <c r="H357" t="n">
         <v>0</v>
@@ -15825,7 +15825,7 @@
         <v>0</v>
       </c>
       <c r="G358" t="n">
-        <v>0.29813</v>
+        <v>0.193578</v>
       </c>
       <c r="H358" t="n">
         <v>0</v>
@@ -15868,7 +15868,7 @@
         <v>0</v>
       </c>
       <c r="G359" t="n">
-        <v>0.056185</v>
+        <v>0.044415</v>
       </c>
       <c r="H359" t="n">
         <v>0</v>
@@ -15911,7 +15911,7 @@
         <v>1</v>
       </c>
       <c r="G360" t="n">
-        <v>0.726799</v>
+        <v>0.6306619999999999</v>
       </c>
       <c r="H360" t="n">
         <v>0</v>
@@ -15954,7 +15954,7 @@
         <v>0</v>
       </c>
       <c r="G361" t="n">
-        <v>0.335857</v>
+        <v>0.250853</v>
       </c>
       <c r="H361" t="n">
         <v>0</v>
@@ -15997,7 +15997,7 @@
         <v>1</v>
       </c>
       <c r="G362" t="n">
-        <v>0.984287</v>
+        <v>0.997148</v>
       </c>
       <c r="H362" t="n">
         <v>0</v>
@@ -16040,7 +16040,7 @@
         <v>0</v>
       </c>
       <c r="G363" t="n">
-        <v>0.096604</v>
+        <v>0.097246</v>
       </c>
       <c r="H363" t="n">
         <v>0</v>
@@ -16083,7 +16083,7 @@
         <v>1</v>
       </c>
       <c r="G364" t="n">
-        <v>0.929796</v>
+        <v>0.96733</v>
       </c>
       <c r="H364" t="n">
         <v>1</v>
@@ -16126,7 +16126,7 @@
         <v>0</v>
       </c>
       <c r="G365" t="n">
-        <v>0.166901</v>
+        <v>0.119359</v>
       </c>
       <c r="H365" t="n">
         <v>0</v>
@@ -16169,7 +16169,7 @@
         <v>0</v>
       </c>
       <c r="G366" t="n">
-        <v>0.263451</v>
+        <v>0.183031</v>
       </c>
       <c r="H366" t="n">
         <v>0</v>
@@ -16209,10 +16209,10 @@
         <v>0.002021</v>
       </c>
       <c r="F367" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G367" t="n">
-        <v>0.526396</v>
+        <v>0.447566</v>
       </c>
       <c r="H367" t="n">
         <v>0</v>
@@ -16255,7 +16255,7 @@
         <v>0</v>
       </c>
       <c r="G368" t="n">
-        <v>0.225</v>
+        <v>0.109234</v>
       </c>
       <c r="H368" t="n">
         <v>0</v>
@@ -16298,7 +16298,7 @@
         <v>0</v>
       </c>
       <c r="G369" t="n">
-        <v>0.247912</v>
+        <v>0.174665</v>
       </c>
       <c r="H369" t="n">
         <v>0</v>
@@ -16341,7 +16341,7 @@
         <v>0</v>
       </c>
       <c r="G370" t="n">
-        <v>0.162215</v>
+        <v>0.136017</v>
       </c>
       <c r="H370" t="n">
         <v>0</v>
@@ -16384,7 +16384,7 @@
         <v>1</v>
       </c>
       <c r="G371" t="n">
-        <v>0.915985</v>
+        <v>0.952132</v>
       </c>
       <c r="H371" t="n">
         <v>0</v>
@@ -16427,7 +16427,7 @@
         <v>0</v>
       </c>
       <c r="G372" t="n">
-        <v>0.204832</v>
+        <v>0.101146</v>
       </c>
       <c r="H372" t="n">
         <v>0</v>
@@ -16470,7 +16470,7 @@
         <v>0</v>
       </c>
       <c r="G373" t="n">
-        <v>0.167214</v>
+        <v>0.09356200000000001</v>
       </c>
       <c r="H373" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
         <v>0</v>
       </c>
       <c r="G374" t="n">
-        <v>0.240663</v>
+        <v>0.135395</v>
       </c>
       <c r="H374" t="n">
         <v>0</v>
@@ -16556,7 +16556,7 @@
         <v>0</v>
       </c>
       <c r="G375" t="n">
-        <v>0.174201</v>
+        <v>0.095929</v>
       </c>
       <c r="H375" t="n">
         <v>0</v>
@@ -16599,7 +16599,7 @@
         <v>0</v>
       </c>
       <c r="G376" t="n">
-        <v>0.229771</v>
+        <v>0.219999</v>
       </c>
       <c r="H376" t="n">
         <v>0</v>
@@ -16642,7 +16642,7 @@
         <v>0</v>
       </c>
       <c r="G377" t="n">
-        <v>0.156806</v>
+        <v>0.114871</v>
       </c>
       <c r="H377" t="n">
         <v>0</v>
@@ -16685,7 +16685,7 @@
         <v>0</v>
       </c>
       <c r="G378" t="n">
-        <v>0.348525</v>
+        <v>0.327163</v>
       </c>
       <c r="H378" t="n">
         <v>0</v>
@@ -16728,7 +16728,7 @@
         <v>0</v>
       </c>
       <c r="G379" t="n">
-        <v>0.213329</v>
+        <v>0.212028</v>
       </c>
       <c r="H379" t="n">
         <v>0</v>
@@ -16771,7 +16771,7 @@
         <v>1</v>
       </c>
       <c r="G380" t="n">
-        <v>0.538667</v>
+        <v>0.645655</v>
       </c>
       <c r="H380" t="n">
         <v>1</v>
@@ -16814,7 +16814,7 @@
         <v>0</v>
       </c>
       <c r="G381" t="n">
-        <v>0.303229</v>
+        <v>0.179907</v>
       </c>
       <c r="H381" t="n">
         <v>0</v>
@@ -16857,7 +16857,7 @@
         <v>1</v>
       </c>
       <c r="G382" t="n">
-        <v>0.710411</v>
+        <v>0.786772</v>
       </c>
       <c r="H382" t="n">
         <v>0</v>
@@ -16900,7 +16900,7 @@
         <v>0</v>
       </c>
       <c r="G383" t="n">
-        <v>0.074985</v>
+        <v>0.048443</v>
       </c>
       <c r="H383" t="n">
         <v>0</v>
@@ -16943,7 +16943,7 @@
         <v>0</v>
       </c>
       <c r="G384" t="n">
-        <v>0.127597</v>
+        <v>0.114004</v>
       </c>
       <c r="H384" t="n">
         <v>0</v>
@@ -16986,7 +16986,7 @@
         <v>0</v>
       </c>
       <c r="G385" t="n">
-        <v>0.059728</v>
+        <v>0.056775</v>
       </c>
       <c r="H385" t="n">
         <v>0</v>
@@ -17029,7 +17029,7 @@
         <v>0</v>
       </c>
       <c r="G386" t="n">
-        <v>0.064222</v>
+        <v>0.051831</v>
       </c>
       <c r="H386" t="n">
         <v>0</v>
@@ -17072,7 +17072,7 @@
         <v>0</v>
       </c>
       <c r="G387" t="n">
-        <v>0.209313</v>
+        <v>0.175673</v>
       </c>
       <c r="H387" t="n">
         <v>0</v>
@@ -17115,7 +17115,7 @@
         <v>0</v>
       </c>
       <c r="G388" t="n">
-        <v>0.195428</v>
+        <v>0.187389</v>
       </c>
       <c r="H388" t="n">
         <v>0</v>
@@ -17158,7 +17158,7 @@
         <v>0</v>
       </c>
       <c r="G389" t="n">
-        <v>0.10418</v>
+        <v>0.09318899999999999</v>
       </c>
       <c r="H389" t="n">
         <v>0</v>
@@ -17201,7 +17201,7 @@
         <v>0</v>
       </c>
       <c r="G390" t="n">
-        <v>0.276227</v>
+        <v>0.167474</v>
       </c>
       <c r="H390" t="n">
         <v>0</v>
@@ -17244,7 +17244,7 @@
         <v>0</v>
       </c>
       <c r="G391" t="n">
-        <v>0.220022</v>
+        <v>0.15679</v>
       </c>
       <c r="H391" t="n">
         <v>0</v>
@@ -17287,7 +17287,7 @@
         <v>1</v>
       </c>
       <c r="G392" t="n">
-        <v>0.640827</v>
+        <v>0.625733</v>
       </c>
       <c r="H392" t="n">
         <v>0</v>
@@ -17330,7 +17330,7 @@
         <v>1</v>
       </c>
       <c r="G393" t="n">
-        <v>0.695905</v>
+        <v>0.611753</v>
       </c>
       <c r="H393" t="n">
         <v>1</v>
@@ -17373,7 +17373,7 @@
         <v>0</v>
       </c>
       <c r="G394" t="n">
-        <v>0.147326</v>
+        <v>0.112322</v>
       </c>
       <c r="H394" t="n">
         <v>0</v>
@@ -17413,10 +17413,10 @@
         <v>0.075473</v>
       </c>
       <c r="F395" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G395" t="n">
-        <v>0.447135</v>
+        <v>0.715686</v>
       </c>
       <c r="H395" t="n">
         <v>0</v>
@@ -17459,7 +17459,7 @@
         <v>0</v>
       </c>
       <c r="G396" t="n">
-        <v>0.268951</v>
+        <v>0.183957</v>
       </c>
       <c r="H396" t="n">
         <v>0</v>
@@ -17502,7 +17502,7 @@
         <v>1</v>
       </c>
       <c r="G397" t="n">
-        <v>0.8762</v>
+        <v>0.779264</v>
       </c>
       <c r="H397" t="n">
         <v>0</v>
@@ -17545,7 +17545,7 @@
         <v>0</v>
       </c>
       <c r="G398" t="n">
-        <v>0.230344</v>
+        <v>0.196851</v>
       </c>
       <c r="H398" t="n">
         <v>0</v>
@@ -17588,7 +17588,7 @@
         <v>0</v>
       </c>
       <c r="G399" t="n">
-        <v>0.169468</v>
+        <v>0.108326</v>
       </c>
       <c r="H399" t="n">
         <v>0</v>
@@ -17631,7 +17631,7 @@
         <v>0</v>
       </c>
       <c r="G400" t="n">
-        <v>0.123372</v>
+        <v>0.115805</v>
       </c>
       <c r="H400" t="n">
         <v>0</v>
@@ -17674,7 +17674,7 @@
         <v>0</v>
       </c>
       <c r="G401" t="n">
-        <v>0.323909</v>
+        <v>0.297356</v>
       </c>
       <c r="H401" t="n">
         <v>0</v>
@@ -17717,7 +17717,7 @@
         <v>0</v>
       </c>
       <c r="G402" t="n">
-        <v>0.174369</v>
+        <v>0.118083</v>
       </c>
       <c r="H402" t="n">
         <v>0</v>
@@ -17760,7 +17760,7 @@
         <v>1</v>
       </c>
       <c r="G403" t="n">
-        <v>0.926781</v>
+        <v>0.98935</v>
       </c>
       <c r="H403" t="n">
         <v>0</v>
@@ -17803,7 +17803,7 @@
         <v>0</v>
       </c>
       <c r="G404" t="n">
-        <v>0.124489</v>
+        <v>0.123112</v>
       </c>
       <c r="H404" t="n">
         <v>0</v>
@@ -17846,7 +17846,7 @@
         <v>0</v>
       </c>
       <c r="G405" t="n">
-        <v>0.114109</v>
+        <v>0.082303</v>
       </c>
       <c r="H405" t="n">
         <v>0</v>
@@ -17889,7 +17889,7 @@
         <v>0</v>
       </c>
       <c r="G406" t="n">
-        <v>0.155137</v>
+        <v>0.119882</v>
       </c>
       <c r="H406" t="n">
         <v>0</v>
@@ -17932,7 +17932,7 @@
         <v>1</v>
       </c>
       <c r="G407" t="n">
-        <v>0.639617</v>
+        <v>0.691485</v>
       </c>
       <c r="H407" t="n">
         <v>1</v>
@@ -17975,7 +17975,7 @@
         <v>1</v>
       </c>
       <c r="G408" t="n">
-        <v>0.981218</v>
+        <v>0.995049</v>
       </c>
       <c r="H408" t="n">
         <v>1</v>
@@ -18018,7 +18018,7 @@
         <v>1</v>
       </c>
       <c r="G409" t="n">
-        <v>0.792253</v>
+        <v>0.791032</v>
       </c>
       <c r="H409" t="n">
         <v>0</v>
@@ -18061,7 +18061,7 @@
         <v>0</v>
       </c>
       <c r="G410" t="n">
-        <v>0.09921000000000001</v>
+        <v>0.07051300000000001</v>
       </c>
       <c r="H410" t="n">
         <v>0</v>
@@ -18104,7 +18104,7 @@
         <v>1</v>
       </c>
       <c r="G411" t="n">
-        <v>0.917726</v>
+        <v>0.916539</v>
       </c>
       <c r="H411" t="n">
         <v>0</v>
@@ -18147,7 +18147,7 @@
         <v>1</v>
       </c>
       <c r="G412" t="n">
-        <v>0.930044</v>
+        <v>0.959819</v>
       </c>
       <c r="H412" t="n">
         <v>0</v>
@@ -18190,7 +18190,7 @@
         <v>0</v>
       </c>
       <c r="G413" t="n">
-        <v>0.142654</v>
+        <v>0.069795</v>
       </c>
       <c r="H413" t="n">
         <v>0</v>
@@ -18233,7 +18233,7 @@
         <v>1</v>
       </c>
       <c r="G414" t="n">
-        <v>0.819018</v>
+        <v>0.724905</v>
       </c>
       <c r="H414" t="n">
         <v>0</v>
